--- a/download/sample_report_salon.xlsx
+++ b/download/sample_report_salon.xlsx
@@ -7,10 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Service Analysis" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Staff Performance" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommendations" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Insights" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommendations" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,11 +20,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="AED #,##0"/>
-    <numFmt numFmtId="165" formatCode="0.0%"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0"/>
-    <numFmt numFmtId="167" formatCode="0.0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -40,18 +39,13 @@
     </font>
     <font>
       <name val="Noto Sans CJK SC"/>
-      <color rgb="002C2C2C"/>
-      <sz val="11"/>
+      <color rgb="00808080"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Noto Sans CJK SC"/>
       <color rgb="002C2C2C"/>
       <sz val="22"/>
-    </font>
-    <font>
-      <name val="Noto Sans CJK SC"/>
-      <color rgb="00808080"/>
-      <sz val="9"/>
     </font>
     <font>
       <name val="Noto Sans CJK SC"/>
@@ -61,6 +55,11 @@
     <font>
       <name val="Noto Sans CJK SC"/>
       <color rgb="001A1A1A"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Noto Sans CJK SC"/>
+      <color rgb="002C2C2C"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -114,76 +113,77 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="4" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="6" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="6" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -192,11 +192,11 @@
   <dxfs count="3">
     <dxf>
       <font>
-        <color rgb="001B7D46"/>
+        <color rgb="00C0392B"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="00E8F5E9"/>
+          <bgColor rgb="00FDEDEC"/>
         </patternFill>
       </fill>
     </dxf>
@@ -212,11 +212,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="00C0392B"/>
+        <color rgb="001B7D46"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="00FDEDEC"/>
+          <bgColor rgb="00E8F5E9"/>
         </patternFill>
       </fill>
     </dxf>
@@ -327,29 +327,27 @@
           <idx val="0"/>
           <order val="0"/>
           <tx>
-            <strRef>
-              <f>'Dashboard'!C8</f>
-            </strRef>
+            <v>Revenue</v>
           </tx>
           <spPr>
             <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="1B2A4A"/>
+              <a:srgbClr val="2C2C2C"/>
             </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:solidFill>
-                <a:srgbClr val="1B2A4A"/>
+                <a:srgbClr val="2C2C2C"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Dashboard'!$B$9:$B$12</f>
+              <f>'Executive Summary'!$B$8:$B$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$C$9:$C$12</f>
+              <f>'Executive Summary'!$C$7:$C$13</f>
             </numRef>
           </val>
         </ser>
@@ -357,29 +355,27 @@
           <idx val="1"/>
           <order val="1"/>
           <tx>
-            <strRef>
-              <f>'Dashboard'!D8</f>
-            </strRef>
+            <v>Expenses</v>
           </tx>
           <spPr>
             <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="D4820A"/>
+              <a:srgbClr val="4A4A4A"/>
             </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:solidFill>
-                <a:srgbClr val="D4820A"/>
+                <a:srgbClr val="4A4A4A"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Dashboard'!$B$9:$B$12</f>
+              <f>'Executive Summary'!$B$8:$B$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$D$9:$D$12</f>
+              <f>'Executive Summary'!$D$7:$D$13</f>
             </numRef>
           </val>
         </ser>
@@ -394,28 +390,6 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0">
-                    <a:latin typeface="Noto Sans CJK SC"/>
-                    <a:ea typeface="Noto Sans CJK SC"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr sz="1000" b="0">
-                    <a:latin typeface="Noto Sans CJK SC"/>
-                    <a:ea typeface="Noto Sans CJK SC"/>
-                  </a:rPr>
-                  <a:t>Month</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="100"/>
@@ -445,6 +419,178 @@
                     <a:ea typeface="Noto Sans CJK SC"/>
                   </a:rPr>
                   <a:t>AED</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+          <txPr>
+            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000"/>
+            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:pPr>
+                <a:defRPr sz="1000" b="0">
+                  <a:latin typeface="Noto Sans CJK SC"/>
+                  <a:ea typeface="Noto Sans CJK SC"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:r>
+                <a:t/>
+              </a:r>
+            </a:p>
+          </txPr>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1200" b="0">
+                <a:latin typeface="Noto Sans CJK SC"/>
+                <a:ea typeface="Noto Sans CJK SC"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1200" b="0">
+                <a:latin typeface="Noto Sans CJK SC"/>
+                <a:ea typeface="Noto Sans CJK SC"/>
+              </a:rPr>
+              <a:t>New vs Returning Clients</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>New Clients</v>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="2C2C2C"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="2C2C2C"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Client Insights'!$B$31:$B$36</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Client Insights'!$C$30:$C$36</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>Returning Clients</v>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="4A4A4A"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="4A4A4A"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Client Insights'!$B$31:$B$36</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Client Insights'!$D$30:$D$36</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0">
+                    <a:latin typeface="Noto Sans CJK SC"/>
+                    <a:ea typeface="Noto Sans CJK SC"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr sz="1000" b="0">
+                    <a:latin typeface="Noto Sans CJK SC"/>
+                    <a:ea typeface="Noto Sans CJK SC"/>
+                  </a:rPr>
+                  <a:t>Clients</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -511,17 +657,15 @@
           <idx val="0"/>
           <order val="0"/>
           <tx>
-            <strRef>
-              <f>'Dashboard'!F8</f>
-            </strRef>
+            <v>Profit Margin</v>
           </tx>
           <spPr>
             <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="1B7D46"/>
+              <a:srgbClr val="2C2C2C"/>
             </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:solidFill>
-                <a:srgbClr val="1B7D46"/>
+                <a:srgbClr val="2C2C2C"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -536,12 +680,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Dashboard'!$B$9:$B$12</f>
+              <f>'Executive Summary'!$B$8:$B$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$F$9:$F$12</f>
+              <f>'Executive Summary'!$E$7:$E$13</f>
             </numRef>
           </val>
         </ser>
@@ -554,28 +698,6 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0">
-                    <a:latin typeface="Noto Sans CJK SC"/>
-                    <a:ea typeface="Noto Sans CJK SC"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr sz="1000" b="0">
-                    <a:latin typeface="Noto Sans CJK SC"/>
-                    <a:ea typeface="Noto Sans CJK SC"/>
-                  </a:rPr>
-                  <a:t>Month</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="100"/>
@@ -624,7 +746,6 @@
             </a:p>
           </txPr>
         </title>
-        <numFmt formatCode="0%" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
@@ -659,7 +780,143 @@
                 <a:latin typeface="Noto Sans CJK SC"/>
                 <a:ea typeface="Noto Sans CJK SC"/>
               </a:rPr>
-              <a:t>Revenue Share by Service</a:t>
+              <a:t>Monthly Bookings Trend</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>Bookings</v>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="2C2C2C"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="2C2C2C"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Executive Summary'!$B$8:$B$13</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Executive Summary'!$G$7:$G$13</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0">
+                    <a:latin typeface="Noto Sans CJK SC"/>
+                    <a:ea typeface="Noto Sans CJK SC"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr sz="1000" b="0">
+                    <a:latin typeface="Noto Sans CJK SC"/>
+                    <a:ea typeface="Noto Sans CJK SC"/>
+                  </a:rPr>
+                  <a:t>Bookings</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+          <txPr>
+            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000"/>
+            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:pPr>
+                <a:defRPr sz="1000" b="0">
+                  <a:latin typeface="Noto Sans CJK SC"/>
+                  <a:ea typeface="Noto Sans CJK SC"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:r>
+                <a:t/>
+              </a:r>
+            </a:p>
+          </txPr>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1200" b="0">
+                <a:latin typeface="Noto Sans CJK SC"/>
+                <a:ea typeface="Noto Sans CJK SC"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1200" b="0">
+                <a:latin typeface="Noto Sans CJK SC"/>
+                <a:ea typeface="Noto Sans CJK SC"/>
+              </a:rPr>
+              <a:t>Revenue by Service</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -753,22 +1010,50 @@
               </a:ln>
             </spPr>
           </dPt>
+          <dPt>
+            <idx val="7"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="6B6B6B"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="8"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="8B0000"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="9"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="808080"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
           <cat>
             <numRef>
-              <f>'Service Analysis'!$B$5:$B$11</f>
+              <f>'Service Analysis'!$B$5:$B$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Service Analysis'!$D$5:$D$11</f>
+              <f>'Service Analysis'!$E$4:$E$14</f>
             </numRef>
           </val>
         </ser>
-        <dLbls>
-          <showVal val="0"/>
-          <showCatName val="0"/>
-          <showPercent val="1"/>
-        </dLbls>
         <firstSliceAng val="0"/>
       </pieChart>
     </plotArea>
@@ -781,7 +1066,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
@@ -815,29 +1100,27 @@
           <idx val="0"/>
           <order val="0"/>
           <tx>
-            <strRef>
-              <f>'Service Analysis'!C4</f>
-            </strRef>
+            <v>Bookings</v>
           </tx>
           <spPr>
             <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="1B2A4A"/>
+              <a:srgbClr val="2C2C2C"/>
             </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:solidFill>
-                <a:srgbClr val="1B2A4A"/>
+                <a:srgbClr val="2C2C2C"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Service Analysis'!$B$5:$B$11</f>
+              <f>'Service Analysis'!$B$5:$B$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Service Analysis'!$C$5:$C$11</f>
+              <f>'Service Analysis'!$D$4:$D$14</f>
             </numRef>
           </val>
         </ser>
@@ -914,7 +1197,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
@@ -934,7 +1217,7 @@
                 <a:latin typeface="Noto Sans CJK SC"/>
                 <a:ea typeface="Noto Sans CJK SC"/>
               </a:rPr>
-              <a:t>Revenue by Staff Member</a:t>
+              <a:t>Utilization by Service</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -942,35 +1225,33 @@
     </title>
     <plotArea>
       <barChart>
-        <barDir val="bar"/>
+        <barDir val="col"/>
         <grouping val="clustered"/>
         <ser>
           <idx val="0"/>
           <order val="0"/>
           <tx>
-            <strRef>
-              <f>'Staff Performance'!E4</f>
-            </strRef>
+            <v>Utilization %</v>
           </tx>
           <spPr>
             <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="1B2A4A"/>
+              <a:srgbClr val="2C2C2C"/>
             </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:solidFill>
-                <a:srgbClr val="1B2A4A"/>
+                <a:srgbClr val="2C2C2C"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Staff Performance'!$B$5:$B$11</f>
+              <f>'Service Analysis'!$B$5:$B$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Staff Performance'!$E$5:$E$11</f>
+              <f>'Service Analysis'!$H$4:$H$14</f>
             </numRef>
           </val>
         </ser>
@@ -985,10 +1266,153 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0">
+                    <a:latin typeface="Noto Sans CJK SC"/>
+                    <a:ea typeface="Noto Sans CJK SC"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr sz="1000" b="0">
+                    <a:latin typeface="Noto Sans CJK SC"/>
+                    <a:ea typeface="Noto Sans CJK SC"/>
+                  </a:rPr>
+                  <a:t>Utilization</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+          <txPr>
+            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000"/>
+            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:pPr>
+                <a:defRPr sz="1000" b="0">
+                  <a:latin typeface="Noto Sans CJK SC"/>
+                  <a:ea typeface="Noto Sans CJK SC"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:r>
+                <a:t/>
+              </a:r>
+            </a:p>
+          </txPr>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1200" b="0">
+                <a:latin typeface="Noto Sans CJK SC"/>
+                <a:ea typeface="Noto Sans CJK SC"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1200" b="0">
+                <a:latin typeface="Noto Sans CJK SC"/>
+                <a:ea typeface="Noto Sans CJK SC"/>
+              </a:rPr>
+              <a:t>Revenue by Staff</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>Revenue (AED)</v>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="2C2C2C"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="2C2C2C"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Staff Performance'!$B$5:$B$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Staff Performance'!$E$4:$E$12</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="80"/>
+        <overlap val="100"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000"/>
               <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="1000" b="0">
@@ -1006,7 +1430,104 @@
               </a:p>
             </rich>
           </tx>
+          <txPr>
+            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000"/>
+            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:pPr>
+                <a:defRPr sz="1000" b="0">
+                  <a:latin typeface="Noto Sans CJK SC"/>
+                  <a:ea typeface="Noto Sans CJK SC"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:r>
+                <a:t/>
+              </a:r>
+            </a:p>
+          </txPr>
         </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1200" b="0">
+                <a:latin typeface="Noto Sans CJK SC"/>
+                <a:ea typeface="Noto Sans CJK SC"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1200" b="0">
+                <a:latin typeface="Noto Sans CJK SC"/>
+                <a:ea typeface="Noto Sans CJK SC"/>
+              </a:rPr>
+              <a:t>Staff Rating Comparison</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>Rating</v>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="2C2C2C"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="2C2C2C"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Staff Performance'!$B$5:$B$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Staff Performance'!$H$4:$H$12</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="80"/>
+        <overlap val="100"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="100"/>
@@ -1019,10 +1540,162 @@
         </scaling>
         <axPos val="l"/>
         <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0">
+                    <a:latin typeface="Noto Sans CJK SC"/>
+                    <a:ea typeface="Noto Sans CJK SC"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr sz="1000" b="0">
+                    <a:latin typeface="Noto Sans CJK SC"/>
+                    <a:ea typeface="Noto Sans CJK SC"/>
+                  </a:rPr>
+                  <a:t>Rating 
+(out of 5)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+          <txPr>
+            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000"/>
+            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:pPr>
+                <a:defRPr sz="1000" b="0">
+                  <a:latin typeface="Noto Sans CJK SC"/>
+                  <a:ea typeface="Noto Sans CJK SC"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:r>
+                <a:t/>
+              </a:r>
+            </a:p>
+          </txPr>
+        </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1200" b="0">
+                <a:latin typeface="Noto Sans CJK SC"/>
+                <a:ea typeface="Noto Sans CJK SC"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1200" b="0">
+                <a:latin typeface="Noto Sans CJK SC"/>
+                <a:ea typeface="Noto Sans CJK SC"/>
+              </a:rPr>
+              <a:t>Revenue by Client Segment</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <pieChart>
+        <varyColors val="1"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <dPt>
+            <idx val="0"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="2C2C2C"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="1"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="4A4A4A"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="2"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="6B6B6B"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="3"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="8B0000"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="4"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="808080"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <cat>
+            <numRef>
+              <f>'Client Insights'!$B$5:$B$9</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Client Insights'!$F$4:$F$9</f>
+            </numRef>
+          </val>
+        </ser>
+        <firstSliceAng val="0"/>
+      </pieChart>
     </plotArea>
     <legend>
       <legendPos val="r"/>
@@ -1039,7 +1712,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>13</row>
+      <row>14</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="6480000" cy="3600000"/>
@@ -1059,12 +1732,154 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4320000" cy="3600000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>30</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4320000" cy="3600000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5040000" cy="3600000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5040000" cy="3600000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>38</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5040000" cy="3600000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
       <col>1</col>
       <colOff>0</colOff>
       <row>25</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="6480000" cy="3600000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>25</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5040000" cy="3600000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -1082,16 +1897,16 @@
 </wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>13</row>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5760000" cy="4320000"/>
+    <ext cx="5040000" cy="3600000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1110,10 +1925,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>26</row>
+      <row>37</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6480000" cy="3600000"/>
+    <ext cx="5760000" cy="3600000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -1123,33 +1938,6 @@
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>14</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="6480000" cy="3600000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="1" name="Chart 1"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1447,174 +2235,298 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:F38"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1"/>
     <row r="2" ht="32" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Luxe Beauty Salon — Monthly Business Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>January 2026 | Dubai, UAE</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="8" customHeight="1"/>
-    <row r="5" ht="40" customHeight="1">
-      <c r="B5" s="3" t="n">
-        <v>98600</v>
-      </c>
+          <t>Luxe Beauty Salon — Executive Dashboard</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="18" customHeight="1">
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Total Expenses</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Net Profit</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Profit Margin</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Total Bookings</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Avg Booking Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="36" customHeight="1">
       <c r="C5" s="3" t="n">
-        <v>72400</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>26200</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>0.266</v>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>Total Revenue</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>Total Expenses</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>Net Profit</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
+        <v>982500</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>614800</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>367700</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>0.3742</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>4280</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>229.56</v>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7" ht="28" customHeight="1">
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Revenue (AED)</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Expenses (AED)</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>Net Profit (AED)</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>Profit Margin</t>
         </is>
       </c>
-    </row>
-    <row r="8" ht="28" customHeight="1">
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Revenue (AED)</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>Expenses (AED)</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>Net Profit (AED)</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>Profit Margin</t>
-        </is>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Bookings</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>Avg Booking (AED)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Aug 2025</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>142800</v>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>92500</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>50300</v>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>0.3522</v>
+      </c>
+      <c r="G8" s="8" t="n">
+        <v>620</v>
+      </c>
+      <c r="H8" s="10" t="n">
+        <v>230.32</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>Sep 2025</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="n">
+        <v>156200</v>
+      </c>
+      <c r="D9" s="12" t="n">
+        <v>99800</v>
+      </c>
+      <c r="E9" s="12" t="n">
+        <v>56400</v>
+      </c>
+      <c r="F9" s="13" t="n">
+        <v>0.3611</v>
+      </c>
+      <c r="G9" s="12" t="n">
+        <v>680</v>
+      </c>
+      <c r="H9" s="14" t="n">
+        <v>229.71</v>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>Oct 2025</t>
         </is>
       </c>
-      <c r="C9" s="8" t="n">
-        <v>82300</v>
-      </c>
-      <c r="D9" s="8" t="n">
-        <v>68500</v>
-      </c>
-      <c r="E9" s="8" t="n">
-        <v>13800</v>
-      </c>
-      <c r="F9" s="9" t="n">
-        <v>0.168</v>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="B10" s="10" t="inlineStr">
+      <c r="C10" s="8" t="n">
+        <v>168400</v>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>105200</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>63200</v>
+      </c>
+      <c r="F10" s="9" t="n">
+        <v>0.3753</v>
+      </c>
+      <c r="G10" s="8" t="n">
+        <v>730</v>
+      </c>
+      <c r="H10" s="10" t="n">
+        <v>230.68</v>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>Nov 2025</t>
         </is>
       </c>
-      <c r="C10" s="11" t="n">
-        <v>88900</v>
-      </c>
-      <c r="D10" s="11" t="n">
-        <v>70200</v>
-      </c>
-      <c r="E10" s="11" t="n">
-        <v>18700</v>
-      </c>
-      <c r="F10" s="12" t="n">
-        <v>0.21</v>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="B11" s="7" t="inlineStr">
+      <c r="C11" s="12" t="n">
+        <v>175600</v>
+      </c>
+      <c r="D11" s="12" t="n">
+        <v>108900</v>
+      </c>
+      <c r="E11" s="12" t="n">
+        <v>66700</v>
+      </c>
+      <c r="F11" s="13" t="n">
+        <v>0.3798</v>
+      </c>
+      <c r="G11" s="12" t="n">
+        <v>760</v>
+      </c>
+      <c r="H11" s="14" t="n">
+        <v>231.05</v>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>Dec 2025</t>
         </is>
       </c>
-      <c r="C11" s="8" t="n">
-        <v>112400</v>
-      </c>
-      <c r="D11" s="8" t="n">
-        <v>76800</v>
-      </c>
-      <c r="E11" s="8" t="n">
-        <v>35600</v>
-      </c>
-      <c r="F11" s="9" t="n">
-        <v>0.317</v>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="B12" s="10" t="inlineStr">
+      <c r="C12" s="8" t="n">
+        <v>172800</v>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>107400</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>65400</v>
+      </c>
+      <c r="F12" s="9" t="n">
+        <v>0.3781</v>
+      </c>
+      <c r="G12" s="8" t="n">
+        <v>845</v>
+      </c>
+      <c r="H12" s="10" t="n">
+        <v>204.5</v>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
       </c>
-      <c r="C12" s="11" t="n">
-        <v>98600</v>
-      </c>
-      <c r="D12" s="11" t="n">
-        <v>72400</v>
-      </c>
-      <c r="E12" s="11" t="n">
-        <v>26200</v>
-      </c>
-      <c r="F12" s="12" t="n">
-        <v>0.266</v>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14"/>
+      <c r="C13" s="12" t="n">
+        <v>166700</v>
+      </c>
+      <c r="D13" s="12" t="n">
+        <v>101000</v>
+      </c>
+      <c r="E13" s="12" t="n">
+        <v>65700</v>
+      </c>
+      <c r="F13" s="13" t="n">
+        <v>0.3941</v>
+      </c>
+      <c r="G13" s="12" t="n">
+        <v>645</v>
+      </c>
+      <c r="H13" s="14" t="n">
+        <v>258.45</v>
+      </c>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="n">
+        <v>982500</v>
+      </c>
+      <c r="D14" s="16" t="n">
+        <v>614800</v>
+      </c>
+      <c r="E14" s="16" t="n">
+        <v>367700</v>
+      </c>
+      <c r="F14" s="17" t="n">
+        <v>0.3742</v>
+      </c>
+      <c r="G14" s="16" t="n">
+        <v>4280</v>
+      </c>
+      <c r="H14" s="18" t="n">
+        <v>229.56</v>
+      </c>
+    </row>
     <row r="15"/>
     <row r="16"/>
     <row r="17"/>
@@ -1632,24 +2544,17 @@
     <row r="29"/>
     <row r="30"/>
     <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38">
-      <c r="B38" s="13" t="inlineStr">
+    <row r="32" ht="20" customHeight="1">
+      <c r="B32" s="19" t="inlineStr">
         <is>
           <t>Prepared by Ahmed Ali | Data Analysis Services | ahmed-ali-ops.vercel.app</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B38:F38"/>
+  <mergeCells count="2">
+    <mergeCell ref="B32:M32"/>
+    <mergeCell ref="B2:M2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1662,23 +2567,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:G39"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1"/>
     <row r="2" ht="32" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Revenue by Service — January 2026</t>
+          <t>Service Performance — January 2026</t>
         </is>
       </c>
     </row>
@@ -1691,27 +2599,37 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
           <t>Bookings</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>Revenue (AED)</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>Avg Price (AED)</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Duration (min)</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Utilization %</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
         <is>
           <t>% of Revenue</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>Utilization</t>
         </is>
       </c>
     </row>
@@ -1721,42 +2639,58 @@
           <t>Hair Coloring</t>
         </is>
       </c>
-      <c r="C5" s="8" t="n">
-        <v>180</v>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Hair</t>
+        </is>
       </c>
       <c r="D5" s="8" t="n">
-        <v>27000</v>
+        <v>380</v>
       </c>
       <c r="E5" s="8" t="n">
+        <v>114000</v>
+      </c>
+      <c r="F5" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="G5" s="8" t="n">
+        <v>120</v>
+      </c>
+      <c r="H5" s="9" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I5" s="9" t="n">
+        <v>0.1368</v>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>Haircut &amp; Styling</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>Hair</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="n">
+        <v>520</v>
+      </c>
+      <c r="E6" s="12" t="n">
+        <v>78000</v>
+      </c>
+      <c r="F6" s="14" t="n">
         <v>150</v>
       </c>
-      <c r="F5" s="9" t="n">
-        <v>0.274</v>
-      </c>
-      <c r="G5" s="9" t="n">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>Haircut &amp; Styling</t>
-        </is>
-      </c>
-      <c r="C6" s="11" t="n">
-        <v>320</v>
-      </c>
-      <c r="D6" s="11" t="n">
-        <v>19200</v>
-      </c>
-      <c r="E6" s="11" t="n">
-        <v>60</v>
-      </c>
-      <c r="F6" s="12" t="n">
-        <v>0.195</v>
-      </c>
       <c r="G6" s="12" t="n">
-        <v>0.9</v>
+        <v>45</v>
+      </c>
+      <c r="H6" s="13" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="I6" s="13" t="n">
+        <v>0.0936</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -1765,42 +2699,58 @@
           <t>Bridal Package</t>
         </is>
       </c>
-      <c r="C7" s="8" t="n">
-        <v>12</v>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Bridal</t>
+        </is>
       </c>
       <c r="D7" s="8" t="n">
-        <v>16800</v>
+        <v>85</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>1400</v>
-      </c>
-      <c r="F7" s="9" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="G7" s="9" t="n">
-        <v>1</v>
+        <v>127500</v>
+      </c>
+      <c r="F7" s="10" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G7" s="8" t="n">
+        <v>360</v>
+      </c>
+      <c r="H7" s="9" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I7" s="9" t="n">
+        <v>0.153</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>Facial Treatment</t>
         </is>
       </c>
-      <c r="C8" s="11" t="n">
-        <v>210</v>
-      </c>
-      <c r="D8" s="11" t="n">
-        <v>12600</v>
-      </c>
-      <c r="E8" s="11" t="n">
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>Skin Care</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="n">
+        <v>290</v>
+      </c>
+      <c r="E8" s="12" t="n">
+        <v>58000</v>
+      </c>
+      <c r="F8" s="14" t="n">
+        <v>200</v>
+      </c>
+      <c r="G8" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="F8" s="12" t="n">
-        <v>0.128</v>
-      </c>
-      <c r="G8" s="12" t="n">
-        <v>0.72</v>
+      <c r="H8" s="13" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="I8" s="13" t="n">
+        <v>0.0696</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -1809,42 +2759,58 @@
           <t>Manicure &amp; Pedicure</t>
         </is>
       </c>
-      <c r="C9" s="8" t="n">
-        <v>280</v>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Nails</t>
+        </is>
       </c>
       <c r="D9" s="8" t="n">
-        <v>11200</v>
+        <v>640</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="F9" s="9" t="n">
-        <v>0.114</v>
-      </c>
-      <c r="G9" s="9" t="n">
-        <v>0.8</v>
+        <v>51200</v>
+      </c>
+      <c r="F9" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="G9" s="8" t="n">
+        <v>45</v>
+      </c>
+      <c r="H9" s="9" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="I9" s="9" t="n">
+        <v>0.0614</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>Keratin Treatment</t>
         </is>
       </c>
-      <c r="C10" s="11" t="n">
-        <v>45</v>
-      </c>
-      <c r="D10" s="11" t="n">
-        <v>8550</v>
-      </c>
-      <c r="E10" s="11" t="n">
-        <v>190</v>
-      </c>
-      <c r="F10" s="12" t="n">
-        <v>0.08699999999999999</v>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>Hair</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="n">
+        <v>195</v>
+      </c>
+      <c r="E10" s="12" t="n">
+        <v>87750</v>
+      </c>
+      <c r="F10" s="14" t="n">
+        <v>450</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.65</v>
+        <v>180</v>
+      </c>
+      <c r="H10" s="13" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="I10" s="13" t="n">
+        <v>0.1053</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -1853,46 +2819,1029 @@
           <t>Henna Design</t>
         </is>
       </c>
-      <c r="C11" s="8" t="n">
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Bridal</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>280</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>33600</v>
+      </c>
+      <c r="F11" s="10" t="n">
+        <v>120</v>
+      </c>
+      <c r="G11" s="8" t="n">
+        <v>90</v>
+      </c>
+      <c r="H11" s="9" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I11" s="9" t="n">
+        <v>0.0403</v>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>Hair Extensions</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>Hair</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="n">
+        <v>110</v>
+      </c>
+      <c r="E12" s="12" t="n">
+        <v>55000</v>
+      </c>
+      <c r="F12" s="14" t="n">
+        <v>500</v>
+      </c>
+      <c r="G12" s="12" t="n">
+        <v>150</v>
+      </c>
+      <c r="H12" s="13" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="I12" s="13" t="n">
+        <v>0.066</v>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Scalp Treatment</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Hair</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="n">
+        <v>160</v>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F13" s="10" t="n">
+        <v>200</v>
+      </c>
+      <c r="G13" s="8" t="n">
         <v>60</v>
       </c>
+      <c r="H13" s="9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I13" s="9" t="n">
+        <v>0.0384</v>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>Makeup</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>Bridal</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="n">
+        <v>420</v>
+      </c>
+      <c r="E14" s="12" t="n">
+        <v>84000</v>
+      </c>
+      <c r="F14" s="14" t="n">
+        <v>200</v>
+      </c>
+      <c r="G14" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="H14" s="13" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I14" s="13" t="n">
+        <v>0.1008</v>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17">
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>Service Category Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Bookings</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>Revenue (AED)</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>% of Revenue</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>Avg Utilization</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Hair</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="n">
+        <v>1365</v>
+      </c>
+      <c r="D19" s="8" t="n">
+        <v>366750</v>
+      </c>
+      <c r="E19" s="9" t="n">
+        <v>0.4398</v>
+      </c>
+      <c r="F19" s="9" t="n">
+        <v>0.775</v>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>Bridal</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="n">
+        <v>785</v>
+      </c>
+      <c r="D20" s="12" t="n">
+        <v>245100</v>
+      </c>
+      <c r="E20" s="13" t="n">
+        <v>0.2941</v>
+      </c>
+      <c r="F20" s="13" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Skin Care</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="n">
+        <v>290</v>
+      </c>
+      <c r="D21" s="8" t="n">
+        <v>58000</v>
+      </c>
+      <c r="E21" s="9" t="n">
+        <v>0.0696</v>
+      </c>
+      <c r="F21" s="9" t="n">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>Nails</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="n">
+        <v>640</v>
+      </c>
+      <c r="D22" s="12" t="n">
+        <v>51200</v>
+      </c>
+      <c r="E22" s="13" t="n">
+        <v>0.0614</v>
+      </c>
+      <c r="F22" s="13" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40" ht="20" customHeight="1">
+      <c r="B40" s="19" t="inlineStr">
+        <is>
+          <t>Prepared by Ahmed Ali | Data Analysis Services | ahmed-ali-ops.vercel.app</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B40:J40"/>
+    <mergeCell ref="B2:J2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15" customHeight="1"/>
+    <row r="2" ht="32" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Staff Performance &amp; Productivity — January 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="28" customHeight="1">
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Clients</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Revenue (AED)</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Avg Ticket (AED)</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Utilization</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Rating</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>Retention Rate</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>Upsell Rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Layla Al Maktoum</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Senior Stylist</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="n">
+        <v>145</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>52200</v>
+      </c>
+      <c r="F5" s="10" t="n">
+        <v>360</v>
+      </c>
+      <c r="G5" s="9" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="H5" s="21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I5" s="9" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J5" s="9" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>Noura Al Ketbi</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>Color Specialist</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="n">
+        <v>120</v>
+      </c>
+      <c r="E6" s="12" t="n">
+        <v>43200</v>
+      </c>
+      <c r="F6" s="14" t="n">
+        <v>360</v>
+      </c>
+      <c r="G6" s="13" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="H6" s="22" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I6" s="13" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J6" s="13" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Sara Ahmed</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Bridal Expert</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>65</v>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>39000</v>
+      </c>
+      <c r="F7" s="10" t="n">
+        <v>600</v>
+      </c>
+      <c r="G7" s="9" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H7" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="I7" s="9" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="J7" s="9" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>Huda Hassan</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>Nail Technician</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="n">
+        <v>180</v>
+      </c>
+      <c r="E8" s="12" t="n">
+        <v>14400</v>
+      </c>
+      <c r="F8" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="G8" s="13" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H8" s="22" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I8" s="13" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J8" s="13" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Mariam Al Suwaidi</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Facial Therapist</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>110</v>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>22000</v>
+      </c>
+      <c r="F9" s="10" t="n">
+        <v>200</v>
+      </c>
+      <c r="G9" s="9" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="H9" s="21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I9" s="9" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="J9" s="9" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>Aisha Mohammed</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>Junior Stylist</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="n">
+        <v>95</v>
+      </c>
+      <c r="E10" s="12" t="n">
+        <v>14250</v>
+      </c>
+      <c r="F10" s="14" t="n">
+        <v>150</v>
+      </c>
+      <c r="G10" s="13" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="H10" s="22" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I10" s="13" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J10" s="13" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Fatima Al Zaabi</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Henna Artist</t>
+        </is>
+      </c>
       <c r="D11" s="8" t="n">
-        <v>3250</v>
+        <v>160</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>54.2</v>
-      </c>
-      <c r="F11" s="9" t="n">
-        <v>0.032</v>
+        <v>19200</v>
+      </c>
+      <c r="F11" s="10" t="n">
+        <v>120</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="12" ht="26" customHeight="1">
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C12" s="15" t="n">
-        <v>1107</v>
-      </c>
-      <c r="D12" s="15" t="n">
-        <v>98600</v>
-      </c>
-      <c r="E12" s="15" t="n">
-        <v>89</v>
-      </c>
-      <c r="F12" s="16" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="H11" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I11" s="9" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J11" s="9" t="n">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>Khadija Omar</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>Makeup Artist</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="n">
+        <v>175</v>
+      </c>
+      <c r="E12" s="12" t="n">
+        <v>35000</v>
+      </c>
+      <c r="F12" s="14" t="n">
+        <v>200</v>
+      </c>
+      <c r="G12" s="13" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H12" s="22" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I12" s="13" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="J12" s="13" t="n">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15">
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>Staff Revenue by Service Category</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Staff Member</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Hair Services</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Bridal Services</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>Skin Care</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>Nails</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Layla Al Maktoum</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="n">
+        <v>31200</v>
+      </c>
+      <c r="D17" s="8" t="n">
+        <v>10500</v>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>4500</v>
+      </c>
+      <c r="F17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="8" t="n">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>Noura Al Ketbi</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="n">
+        <v>36000</v>
+      </c>
+      <c r="D18" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="12" t="n">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Sara Ahmed</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="8" t="n">
+        <v>39000</v>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>Huda Hassan</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="12" t="n">
+        <v>14400</v>
+      </c>
+      <c r="G20" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Mariam Al Suwaidi</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>22000</v>
+      </c>
+      <c r="F21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>Aisha Mohammed</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="n">
+        <v>9500</v>
+      </c>
+      <c r="D22" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="12" t="n">
+        <v>4750</v>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Fatima Al Zaabi</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="8" t="n">
+        <v>8400</v>
+      </c>
+      <c r="E23" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="8" t="n">
+        <v>10800</v>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>Khadija Omar</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="12" t="n">
+        <v>35000</v>
+      </c>
+      <c r="E24" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38" ht="20" customHeight="1">
+      <c r="B38" s="19" t="inlineStr">
+        <is>
+          <t>Prepared by Ahmed Ali | Data Analysis Services | ahmed-ali-ops.vercel.app</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B38:K38"/>
+    <mergeCell ref="B2:K2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I71"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15" customHeight="1"/>
+    <row r="2" ht="32" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Client Analytics — January 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="28" customHeight="1">
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Segment</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Clients</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Avg Spend (AED)</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Visits/Month</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Revenue (AED)</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Retention Rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Regular Monthly</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="n">
+        <v>1850</v>
+      </c>
+      <c r="D5" s="10" t="n">
+        <v>185</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" s="8" t="n">
+        <v>1027875</v>
+      </c>
+      <c r="G5" s="9" t="n">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>Bridal</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="n">
+        <v>280</v>
+      </c>
+      <c r="D6" s="14" t="n">
+        <v>650</v>
+      </c>
+      <c r="E6" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G12" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
+      <c r="F6" s="12" t="n">
+        <v>182000</v>
+      </c>
+      <c r="G6" s="13" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Occasional</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="n">
+        <v>950</v>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>120</v>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" s="8" t="n">
+        <v>228000</v>
+      </c>
+      <c r="G7" s="9" t="n">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>Tourist</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="n">
+        <v>420</v>
+      </c>
+      <c r="D8" s="14" t="n">
+        <v>280</v>
+      </c>
+      <c r="E8" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="12" t="n">
+        <v>117600</v>
+      </c>
+      <c r="G8" s="13" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>VIP</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="n">
+        <v>65</v>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>950</v>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" s="8" t="n">
+        <v>247000</v>
+      </c>
+      <c r="G9" s="9" t="n">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11"/>
+    <row r="12"/>
     <row r="13"/>
     <row r="14"/>
     <row r="15"/>
@@ -1909,18 +3858,442 @@
     <row r="26"/>
     <row r="27"/>
     <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
+    <row r="29">
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>New vs Returning Clients (6-Month Trend)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="28" customHeight="1">
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>New Clients</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>Returning Clients</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>Retention Rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Aug 2025</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="n">
+        <v>185</v>
+      </c>
+      <c r="D31" s="8" t="n">
+        <v>435</v>
+      </c>
+      <c r="E31" s="8" t="n">
+        <v>620</v>
+      </c>
+      <c r="F31" s="9" t="n">
+        <v>0.702</v>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>Sep 2025</t>
+        </is>
+      </c>
+      <c r="C32" s="12" t="n">
+        <v>195</v>
+      </c>
+      <c r="D32" s="12" t="n">
+        <v>485</v>
+      </c>
+      <c r="E32" s="12" t="n">
+        <v>680</v>
+      </c>
+      <c r="F32" s="13" t="n">
+        <v>0.713</v>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>Oct 2025</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="n">
+        <v>210</v>
+      </c>
+      <c r="D33" s="8" t="n">
+        <v>520</v>
+      </c>
+      <c r="E33" s="8" t="n">
+        <v>730</v>
+      </c>
+      <c r="F33" s="9" t="n">
+        <v>0.712</v>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t>Nov 2025</t>
+        </is>
+      </c>
+      <c r="C34" s="12" t="n">
+        <v>225</v>
+      </c>
+      <c r="D34" s="12" t="n">
+        <v>535</v>
+      </c>
+      <c r="E34" s="12" t="n">
+        <v>760</v>
+      </c>
+      <c r="F34" s="13" t="n">
+        <v>0.704</v>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>Dec 2025</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="n">
+        <v>260</v>
+      </c>
+      <c r="D35" s="8" t="n">
+        <v>585</v>
+      </c>
+      <c r="E35" s="8" t="n">
+        <v>845</v>
+      </c>
+      <c r="F35" s="9" t="n">
+        <v>0.6919999999999999</v>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>Jan 2026</t>
+        </is>
+      </c>
+      <c r="C36" s="12" t="n">
+        <v>190</v>
+      </c>
+      <c r="D36" s="12" t="n">
+        <v>455</v>
+      </c>
+      <c r="E36" s="12" t="n">
+        <v>645</v>
+      </c>
+      <c r="F36" s="13" t="n">
+        <v>0.706</v>
+      </c>
+    </row>
     <row r="37"/>
     <row r="38"/>
-    <row r="39">
-      <c r="B39" s="13" t="inlineStr">
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56">
+      <c r="B56" s="20" t="inlineStr">
+        <is>
+          <t>Day &amp; Time Slot Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="28" customHeight="1">
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>Time Slot</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>Bookings</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>Revenue (AED)</t>
+        </is>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>Avg Booking (AED)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="22" customHeight="1">
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C58" s="7" t="inlineStr">
+        <is>
+          <t>9 AM – 12 PM</t>
+        </is>
+      </c>
+      <c r="D58" s="8" t="n">
+        <v>42</v>
+      </c>
+      <c r="E58" s="8" t="n">
+        <v>10920</v>
+      </c>
+      <c r="F58" s="10" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="59" ht="22" customHeight="1">
+      <c r="B59" s="11" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C59" s="11" t="inlineStr">
+        <is>
+          <t>12 PM – 4 PM</t>
+        </is>
+      </c>
+      <c r="D59" s="12" t="n">
+        <v>58</v>
+      </c>
+      <c r="E59" s="12" t="n">
+        <v>15080</v>
+      </c>
+      <c r="F59" s="14" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="60" ht="22" customHeight="1">
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t>4 PM – 9 PM</t>
+        </is>
+      </c>
+      <c r="D60" s="8" t="n">
+        <v>72</v>
+      </c>
+      <c r="E60" s="8" t="n">
+        <v>19440</v>
+      </c>
+      <c r="F60" s="10" t="n">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="61" ht="22" customHeight="1">
+      <c r="B61" s="11" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C61" s="11" t="inlineStr">
+        <is>
+          <t>9 AM – 12 PM</t>
+        </is>
+      </c>
+      <c r="D61" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="E61" s="12" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F61" s="14" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="62" ht="22" customHeight="1">
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="inlineStr">
+        <is>
+          <t>12 PM – 4 PM</t>
+        </is>
+      </c>
+      <c r="D62" s="8" t="n">
+        <v>45</v>
+      </c>
+      <c r="E62" s="8" t="n">
+        <v>11700</v>
+      </c>
+      <c r="F62" s="10" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="63" ht="22" customHeight="1">
+      <c r="B63" s="11" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C63" s="11" t="inlineStr">
+        <is>
+          <t>4 PM – 9 PM</t>
+        </is>
+      </c>
+      <c r="D63" s="12" t="n">
+        <v>55</v>
+      </c>
+      <c r="E63" s="12" t="n">
+        <v>14300</v>
+      </c>
+      <c r="F63" s="14" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="64" ht="22" customHeight="1">
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="inlineStr">
+        <is>
+          <t>10 AM – 5 PM</t>
+        </is>
+      </c>
+      <c r="D64" s="8" t="n">
+        <v>48</v>
+      </c>
+      <c r="E64" s="8" t="n">
+        <v>12000</v>
+      </c>
+      <c r="F64" s="10" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="65" ht="22" customHeight="1">
+      <c r="B65" s="11" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C65" s="11" t="inlineStr">
+        <is>
+          <t>10 AM – 5 PM</t>
+        </is>
+      </c>
+      <c r="D65" s="12" t="n">
+        <v>52</v>
+      </c>
+      <c r="E65" s="12" t="n">
+        <v>13000</v>
+      </c>
+      <c r="F65" s="14" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="66" ht="22" customHeight="1">
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C66" s="7" t="inlineStr">
+        <is>
+          <t>10 AM – 5 PM</t>
+        </is>
+      </c>
+      <c r="D66" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="E66" s="8" t="n">
+        <v>12500</v>
+      </c>
+      <c r="F66" s="10" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="67" ht="22" customHeight="1">
+      <c r="B67" s="11" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C67" s="11" t="inlineStr">
+        <is>
+          <t>10 AM – 9 PM</t>
+        </is>
+      </c>
+      <c r="D67" s="12" t="n">
+        <v>78</v>
+      </c>
+      <c r="E67" s="12" t="n">
+        <v>21060</v>
+      </c>
+      <c r="F67" s="14" t="n">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="68" ht="22" customHeight="1">
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C68" s="7" t="inlineStr">
+        <is>
+          <t>9 AM – 9 PM</t>
+        </is>
+      </c>
+      <c r="D68" s="8" t="n">
+        <v>125</v>
+      </c>
+      <c r="E68" s="8" t="n">
+        <v>35000</v>
+      </c>
+      <c r="F68" s="10" t="n">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71" ht="20" customHeight="1">
+      <c r="B71" s="19" t="inlineStr">
         <is>
           <t>Prepared by Ahmed Ali | Data Analysis Services | ahmed-ali-ops.vercel.app</t>
         </is>
@@ -1928,37 +4301,38 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B39:G39"/>
+    <mergeCell ref="B71:I71"/>
+    <mergeCell ref="B2:I2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:G27"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1"/>
     <row r="2" ht="32" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Staff Performance — January 2026</t>
+          <t>Key Insights &amp; Strategic Recommendations</t>
         </is>
       </c>
     </row>
@@ -1966,398 +4340,279 @@
     <row r="4" ht="28" customHeight="1">
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Staff Name</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Clients Served</t>
+          <t>Insight</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Revenue (AED)</t>
+          <t>Impact</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Avg Ticket (AED)</t>
+          <t>Action Item</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>Rating</t>
+          <t>Priority</t>
         </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Fatima K.</t>
-        </is>
+      <c r="B5" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>Senior Stylist</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="n">
-        <v>95</v>
-      </c>
-      <c r="E5" s="8" t="n">
-        <v>18500</v>
-      </c>
-      <c r="F5" s="17" t="n">
-        <v>194.7</v>
-      </c>
-      <c r="G5" s="18" t="n">
-        <v>4.9</v>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Bridal Package has highest avg price (AED 1,500) and 95% utilization</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Increase bridal package price by 10% and add premium add-ons</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>Noor A.</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>Colorist</t>
-        </is>
-      </c>
-      <c r="D6" s="11" t="n">
-        <v>78</v>
-      </c>
-      <c r="E6" s="11" t="n">
-        <v>15200</v>
-      </c>
-      <c r="F6" s="19" t="n">
-        <v>194.9</v>
-      </c>
-      <c r="G6" s="20" t="n">
-        <v>4.8</v>
+      <c r="B6" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>Staff</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>Sara Ahmed has 5.0 rating and highest retention rate (92%) but serves only 65 clients</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F6" s="11" t="inlineStr">
+        <is>
+          <t>Increase Sara's capacity by assigning junior assistant for bridal prep</t>
+        </is>
+      </c>
+      <c r="G6" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>Sara M.</t>
-        </is>
+      <c r="B7" s="23" t="n">
+        <v>3</v>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>Bridal Specialist</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="E7" s="8" t="n">
-        <v>16800</v>
-      </c>
-      <c r="F7" s="17" t="n">
-        <v>763.6</v>
-      </c>
-      <c r="G7" s="18" t="n">
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>Tourist segment has 20% retention — opportunity for re-engagement</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>Launch digital follow-up campaign with discount for next visit</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="B8" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>Hair Extensions utilization is only 65% — lowest performing service</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F8" s="11" t="inlineStr">
+        <is>
+          <t>Promote extensions with free consultation and before/after showcase</t>
+        </is>
+      </c>
+      <c r="G8" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="B9" s="23" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>Maryam H.</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>Nail Technician</t>
-        </is>
-      </c>
-      <c r="D8" s="11" t="n">
-        <v>120</v>
-      </c>
-      <c r="E8" s="11" t="n">
-        <v>8400</v>
-      </c>
-      <c r="F8" s="19" t="n">
-        <v>70</v>
-      </c>
-      <c r="G8" s="20" t="n">
-        <v>4.7</v>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>Aisha R.</t>
-        </is>
-      </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>Facial Specialist</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="n">
-        <v>88</v>
-      </c>
-      <c r="E9" s="8" t="n">
-        <v>7920</v>
-      </c>
-      <c r="F9" s="17" t="n">
-        <v>90</v>
-      </c>
-      <c r="G9" s="18" t="n">
-        <v>4.6</v>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>Friday and Saturday generate 40% of weekly bookings</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>Add premium pricing for weekend peak slots to maximize revenue per slot</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>Layla S.</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>Junior Stylist</t>
-        </is>
-      </c>
-      <c r="D10" s="11" t="n">
-        <v>65</v>
-      </c>
-      <c r="E10" s="11" t="n">
-        <v>5850</v>
-      </c>
-      <c r="F10" s="19" t="n">
-        <v>90</v>
-      </c>
-      <c r="G10" s="20" t="n">
-        <v>4.5</v>
+      <c r="B10" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>VIP segment (65 clients) generates AED 247K — AED 3,808 avg per client</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F10" s="11" t="inlineStr">
+        <is>
+          <t>Create exclusive VIP membership with priority booking and complimentary services</t>
+        </is>
+      </c>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>Huda B.</t>
-        </is>
+      <c r="B11" s="23" t="n">
+        <v>7</v>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>Henna Artist</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="E11" s="8" t="n">
-        <v>2700</v>
-      </c>
-      <c r="F11" s="17" t="n">
-        <v>54</v>
-      </c>
-      <c r="G11" s="18" t="n">
-        <v>4.8</v>
-      </c>
-    </row>
-    <row r="12" ht="26" customHeight="1">
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D12" s="15" t="n">
-        <v>518</v>
-      </c>
-      <c r="E12" s="15" t="n">
-        <v>75370</v>
-      </c>
-      <c r="F12" s="21" t="n">
-        <v>145.5</v>
-      </c>
-      <c r="G12" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="13" t="inlineStr">
-        <is>
-          <t>Note: Staff revenue does not equal total salon revenue (some bookings have multiple staff)</t>
-        </is>
-      </c>
-    </row>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>Scalp Treatment has 70% utilization — growth potential in hair wellness</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>Partner with dermatologists for referrals and add treatment packages</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="B12" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>New client acquisition dropped 27% in Jan vs Dec</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F12" s="11" t="inlineStr">
+        <is>
+          <t>Launch referral program: existing clients get AED 50 credit for each referral</t>
+        </is>
+      </c>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27">
-      <c r="B27" s="13" t="inlineStr">
-        <is>
-          <t>Prepared by Ahmed Ali | Data Analysis Services | ahmed-ali-ops.vercel.app</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B27:G27"/>
-    <mergeCell ref="B13:G13"/>
-  </mergeCells>
-  <conditionalFormatting sqref="G5:G11">
-    <cfRule type="cellIs" priority="1" operator="greaterThanOrEqual" dxfId="0">
-      <formula>4.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="2" operator="between" dxfId="1">
-      <formula>4.6</formula>
-      <formula>4.79</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="3" operator="lessThan" dxfId="2">
-      <formula>4.6</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A2:D11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="15" customHeight="1"/>
-    <row r="2" ht="32" customHeight="1">
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>Key Insights &amp; Recommendations</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="8" customHeight="1"/>
-    <row r="4" ht="28" customHeight="1">
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Insight</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Priority</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="B5" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>Bridal packages generate AED 1,400 avg ticket — highest ROI. Increase bridal marketing budget by 20%.</t>
-        </is>
-      </c>
-      <c r="D5" s="22" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="B6" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>Keratin treatment utilization is only 65%. Run a promotion to boost bookings.</t>
-        </is>
-      </c>
-      <c r="D6" s="23" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="B7" s="22" t="n">
-        <v>3</v>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>Henna service utilization at 50%. Consider offering henna as add-on to bridal packages.</t>
-        </is>
-      </c>
-      <c r="D7" s="22" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="B8" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>December showed 31.7% margin (wedding season). Plan staffing for Dec 2026 peak.</t>
-        </is>
-      </c>
-      <c r="D8" s="23" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="B9" s="22" t="n">
-        <v>5</v>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>Facial treatments have room for growth (72% utilization). Partner with skincare brands for events.</t>
-        </is>
-      </c>
-      <c r="D9" s="22" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="B11" s="13" t="inlineStr">
+    <row r="15" ht="20" customHeight="1">
+      <c r="B15" s="19" t="inlineStr">
         <is>
           <t>Prepared by Ahmed Ali | Data Analysis Services | ahmed-ali-ops.vercel.app</t>
         </is>
@@ -2365,18 +4620,26 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B15:H15"/>
   </mergeCells>
-  <conditionalFormatting sqref="D5:D9">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="2">
+  <conditionalFormatting sqref="G5:G12">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"High"</formula>
     </cfRule>
     <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
       <formula>"Medium"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"Low"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E5:E12">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="0">
+      <formula>"High"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="1">
+      <formula>"Medium"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
